--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J105-EnsembleDiplome-RASS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J105-EnsembleDiplome-RASS.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="1549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="1551">
   <si>
     <t>Property</t>
   </si>
@@ -49,7 +49,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250828120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -76,7 +76,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-28T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1528,31 +1528,31 @@
     <t>DIP324</t>
   </si>
   <si>
-    <t>Master mention psychologie clinique, psychopathologie et psychologie de la santé</t>
+    <t>Licence + Master mention psychologie clinique, psychopatho et psycho santé + Attest stage</t>
   </si>
   <si>
     <t>DIP325</t>
   </si>
   <si>
-    <t>Master mention psychologie sociale, du travail et des organisations</t>
+    <t>Licence + Master mention psychologie sociale, du travail et des organisations + Attest stage</t>
   </si>
   <si>
     <t>DIP326</t>
   </si>
   <si>
-    <t>Master mention psychologie de l'éducation et de la formation</t>
+    <t>Licence + Master mention psychologie de l'éducation et de la formation + Attest stage</t>
   </si>
   <si>
     <t>DIP327</t>
   </si>
   <si>
-    <t>Master mention psychopathologie clinique psychanalytique</t>
+    <t>Licence + Master mention psychologie: psychopatho clinique psychanalytique + Attest stage</t>
   </si>
   <si>
     <t>DIP328</t>
   </si>
   <si>
-    <t>Master de Psychanalyse</t>
+    <t>Diplôme de niveau Master en psychanalyse</t>
   </si>
   <si>
     <t>DIP329</t>
@@ -4670,6 +4670,12 @@
   </si>
   <si>
     <t>FST Urgences pédiatriques</t>
+  </si>
+  <si>
+    <t>FST27</t>
+  </si>
+  <si>
+    <t>FST Innovation et recherche en sciences biologiques et pharmaceutiques</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R348-FormationSpecialiseeTransversale/FHIR/TRE-R348-FormationSpecialiseeTransversale</t>
@@ -6684,7 +6690,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -6909,18 +6915,26 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>401</v>
+        <v>1548</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>401</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="B29" t="s" s="2">
-        <v>1548</v>
+      <c r="B30" t="s" s="2">
+        <v>1550</v>
       </c>
     </row>
   </sheetData>
